--- a/data/trans_orig/P21-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2007</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>561412</t>
+          <t>560654</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>600825</t>
+          <t>600749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>530242</t>
+          <t>529948</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>571362</t>
+          <t>571637</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1102713</t>
+          <t>1103658</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1158276</t>
+          <t>1161562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,08%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10335</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>92301</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131434</t>
+          <t>132096</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>114556</t>
+          <t>114850</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155156</t>
+          <t>155661</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>219363</t>
+          <t>217590</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>276305</t>
+          <t>273919</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>750765</t>
+          <t>750896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>798522</t>
+          <t>800466</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>655360</t>
+          <t>655732</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>713138</t>
+          <t>715508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1419990</t>
+          <t>1421933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1494390</t>
+          <t>1498745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,65%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17372</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17828</t>
+          <t>18701</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10906</t>
+          <t>11128</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30050</t>
+          <t>30316</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155378</t>
+          <t>153415</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202004</t>
+          <t>202307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>246253</t>
+          <t>244467</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>301560</t>
+          <t>303258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>419546</t>
+          <t>411967</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>491611</t>
+          <t>488146</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>531543</t>
+          <t>534219</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>575033</t>
+          <t>576157</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>484805</t>
+          <t>483347</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>530288</t>
+          <t>528541</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1030605</t>
+          <t>1031427</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1092806</t>
+          <t>1094472</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,34%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17735</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25766</t>
+          <t>25215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97953</t>
+          <t>98253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>139405</t>
+          <t>138576</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143043</t>
+          <t>145448</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187166</t>
+          <t>190408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254870</t>
+          <t>254135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>314873</t>
+          <t>315123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>783654</t>
+          <t>783097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>825656</t>
+          <t>823263</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>781883</t>
+          <t>784024</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>836771</t>
+          <t>837277</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1580335</t>
+          <t>1580615</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1650040</t>
+          <t>1648420</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22067</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10655</t>
+          <t>10038</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27640</t>
+          <t>26964</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111732</t>
+          <t>114014</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153615</t>
+          <t>154686</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>188463</t>
+          <t>189167</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>242543</t>
+          <t>240383</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>313920</t>
+          <t>316306</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>382780</t>
+          <t>381111</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2668274</t>
+          <t>2672920</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2754391</t>
+          <t>2760435</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2504533</t>
+          <t>2505396</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2603268</t>
+          <t>2603393</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5204782</t>
+          <t>5203123</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5335960</t>
+          <t>5334483</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30331</t>
+          <t>31592</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>25187</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49541</t>
+          <t>50323</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41146</t>
+          <t>41643</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>70485</t>
+          <t>71984</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>503666</t>
+          <t>496109</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>586503</t>
+          <t>585024</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>737331</t>
+          <t>742014</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>835566</t>
+          <t>839809</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1262273</t>
+          <t>1265979</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1389605</t>
+          <t>1392780</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2012</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>540762</t>
+          <t>537540</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>580511</t>
+          <t>583887</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>478506</t>
+          <t>478422</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>525576</t>
+          <t>526132</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1027987</t>
+          <t>1034252</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1096575</t>
+          <t>1096271</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,82 +3373,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5294</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11882</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>12698</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>6564</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>21090</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5294</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2080</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>11791</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>12698</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>6998</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>22081</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114871</t>
+          <t>113308</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>155271</t>
+          <t>157597</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>164904</t>
+          <t>165963</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>211514</t>
+          <t>213508</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>291317</t>
+          <t>290932</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>359797</t>
+          <t>352708</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>760235</t>
+          <t>760767</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>816418</t>
+          <t>814915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>703296</t>
+          <t>699690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>761192</t>
+          <t>761299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1481137</t>
+          <t>1480679</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1558193</t>
+          <t>1564145</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36077</t>
+          <t>36928</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>44230</t>
+          <t>44530</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>194866</t>
+          <t>195272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>250269</t>
+          <t>249461</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>248345</t>
+          <t>248825</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>303632</t>
+          <t>307588</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>462106</t>
+          <t>456495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>538344</t>
+          <t>538029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>546816</t>
+          <t>546964</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>599375</t>
+          <t>598257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>490081</t>
+          <t>491544</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>544619</t>
+          <t>545495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1056933</t>
+          <t>1052134</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1132723</t>
+          <t>1126099</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,42%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>18498</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31928</t>
+          <t>31473</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148018</t>
+          <t>150810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200863</t>
+          <t>200879</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223377</t>
+          <t>219837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>277152</t>
+          <t>274437</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>379489</t>
+          <t>386073</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>454783</t>
+          <t>460021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>770268</t>
+          <t>769457</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>814597</t>
+          <t>816214</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>793302</t>
+          <t>795249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>848951</t>
+          <t>848557</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1580147</t>
+          <t>1579378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1648961</t>
+          <t>1653600</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,86%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18750</t>
+          <t>16969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22466</t>
+          <t>22093</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,42 +4776,42 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>23627</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>15221</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>34578</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>0,76%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>23627</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>15601</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>34477</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>122578</t>
+          <t>119311</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>164979</t>
+          <t>165864</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>187275</t>
+          <t>189808</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>243157</t>
+          <t>240047</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>321240</t>
+          <t>319982</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>391324</t>
+          <t>391860</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2664835</t>
+          <t>2665805</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2765436</t>
+          <t>2763114</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2517014</t>
+          <t>2512312</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2627981</t>
+          <t>2626234</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5216196</t>
+          <t>5214702</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5363595</t>
+          <t>5365185</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23895</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48047</t>
+          <t>47808</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40800</t>
+          <t>40974</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70044</t>
+          <t>70123</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>71010</t>
+          <t>71344</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>110159</t>
+          <t>108278</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>624815</t>
+          <t>625178</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>722862</t>
+          <t>719993</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>875423</t>
+          <t>876962</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>984256</t>
+          <t>986990</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1530467</t>
+          <t>1520447</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1673651</t>
+          <t>1673178</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2016</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>547421</t>
+          <t>547016</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>585401</t>
+          <t>584302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>505256</t>
+          <t>507657</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>550703</t>
+          <t>551391</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1069813</t>
+          <t>1066658</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1124440</t>
+          <t>1127558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,79%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19144</t>
+          <t>18676</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17253</t>
+          <t>17095</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12881</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31156</t>
+          <t>30990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77680</t>
+          <t>77726</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113295</t>
+          <t>113390</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>112149</t>
+          <t>111746</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>154440</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>202522</t>
+          <t>197165</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>255734</t>
+          <t>257098</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>813697</t>
+          <t>812707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>864298</t>
+          <t>864693</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>794228</t>
+          <t>792572</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>848640</t>
+          <t>846938</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1628334</t>
+          <t>1622955</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1704341</t>
+          <t>1697964</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10658</t>
+          <t>9886</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27701</t>
+          <t>27355</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31074</t>
+          <t>30886</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24725</t>
+          <t>23535</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50205</t>
+          <t>49967</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135746</t>
+          <t>134675</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181497</t>
+          <t>183074</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>172249</t>
+          <t>176070</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>226526</t>
+          <t>226554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>321129</t>
+          <t>323469</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>392319</t>
+          <t>396065</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>607021</t>
+          <t>606367</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>649474</t>
+          <t>651193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>606995</t>
+          <t>604415</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>650652</t>
+          <t>649604</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1225891</t>
+          <t>1225419</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1291967</t>
+          <t>1288721</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>18602</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28432</t>
+          <t>27560</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103467</t>
+          <t>101471</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143709</t>
+          <t>145588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122764</t>
+          <t>122980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165501</t>
+          <t>167009</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235926</t>
+          <t>237821</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>300810</t>
+          <t>299946</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>754586</t>
+          <t>757443</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>801936</t>
+          <t>804105</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>765641</t>
+          <t>762587</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>822028</t>
+          <t>818547</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1533834</t>
+          <t>1538079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1610089</t>
+          <t>1612116</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19947</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14083</t>
+          <t>14702</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34614</t>
+          <t>34163</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23946</t>
+          <t>23495</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47718</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>123230</t>
+          <t>121378</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>169098</t>
+          <t>166309</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>199698</t>
+          <t>199206</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>252925</t>
+          <t>255584</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>335352</t>
+          <t>334110</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>406098</t>
+          <t>405517</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2775333</t>
+          <t>2778181</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2865037</t>
+          <t>2862451</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2728136</t>
+          <t>2720750</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2828072</t>
+          <t>2823808</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5528400</t>
+          <t>5529828</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5663983</t>
+          <t>5664986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32510</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>59651</t>
+          <t>61269</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45008</t>
+          <t>44524</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78036</t>
+          <t>78948</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,47 +7744,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>106763</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>87875</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>132022</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>106763</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>87126</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>130455</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>474563</t>
+          <t>479418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>559970</t>
+          <t>559088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>652560</t>
+          <t>655834</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>747184</t>
+          <t>758355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1152672</t>
+          <t>1156904</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1285740</t>
+          <t>1286180</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2023</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>479420</t>
+          <t>482300</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>525582</t>
+          <t>525958</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>513856</t>
+          <t>514849</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>550683</t>
+          <t>550313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1010388</t>
+          <t>1008949</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1065798</t>
+          <t>1061880</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>345</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7435</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>9744</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107308</t>
+          <t>106418</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152376</t>
+          <t>149732</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>120963</t>
+          <t>122601</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>157354</t>
+          <t>158019</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>238658</t>
+          <t>241879</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>293670</t>
+          <t>295699</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>911902</t>
+          <t>914314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1075251</t>
+          <t>1090663</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>693724</t>
+          <t>697187</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>742478</t>
+          <t>744320</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1627326</t>
+          <t>1627541</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1844479</t>
+          <t>1863026</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10585</t>
+          <t>10344</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16507</t>
+          <t>16353</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115553</t>
+          <t>100687</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>276660</t>
+          <t>275169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>208453</t>
+          <t>207005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>256583</t>
+          <t>253791</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296107</t>
+          <t>279365</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>511138</t>
+          <t>511133</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>540523</t>
+          <t>538212</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>588051</t>
+          <t>586950</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>254343</t>
+          <t>286147</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>701906</t>
+          <t>701578</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>746844</t>
+          <t>769195</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1275737</t>
+          <t>1279312</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,28%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>490</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14131</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110599</t>
+          <t>112096</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159394</t>
+          <t>161287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224806</t>
+          <t>224927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>673971</t>
+          <t>640082</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>350683</t>
+          <t>347029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>878864</t>
+          <t>860051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>52,63%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>705406</t>
+          <t>703844</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>757337</t>
+          <t>755402</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>782387</t>
+          <t>783400</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>869247</t>
+          <t>872514</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1505367</t>
+          <t>1503899</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1603756</t>
+          <t>1600030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>9923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24947</t>
+          <t>24176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17461</t>
+          <t>17490</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35565</t>
+          <t>35584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161554</t>
+          <t>160829</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>212262</t>
+          <t>212387</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>210514</t>
+          <t>207389</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>291742</t>
+          <t>289500</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>391183</t>
+          <t>396334</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>486093</t>
+          <t>488440</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2708867</t>
+          <t>2702110</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2931030</t>
+          <t>2933540</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2074693</t>
+          <t>2118192</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2781717</t>
+          <t>2779790</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4822798</t>
+          <t>4788190</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5607577</t>
+          <t>5585163</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28832</t>
+          <t>29856</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19935</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36284</t>
+          <t>37392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>36686</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>61259</t>
+          <t>61174</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>512316</t>
+          <t>509372</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>729500</t>
+          <t>735800</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>843702</t>
+          <t>843271</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1555264</t>
+          <t>1507931</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1459473</t>
+          <t>1479337</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2251053</t>
+          <t>2298887</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>560654</t>
+          <t>561862</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>600749</t>
+          <t>598815</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>529948</t>
+          <t>529277</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>571637</t>
+          <t>571251</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1103658</t>
+          <t>1102924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1161562</t>
+          <t>1159521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,94%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5862</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92301</t>
+          <t>94575</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132096</t>
+          <t>130690</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>114850</t>
+          <t>113739</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155661</t>
+          <t>154686</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>217590</t>
+          <t>218752</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>273919</t>
+          <t>275432</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>750896</t>
+          <t>747337</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>800466</t>
+          <t>799784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>655732</t>
+          <t>655114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>715508</t>
+          <t>712248</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1421933</t>
+          <t>1420222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1498745</t>
+          <t>1496084</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,51%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17372</t>
+          <t>17033</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18701</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11128</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30316</t>
+          <t>29437</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153415</t>
+          <t>154069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202307</t>
+          <t>203963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>244467</t>
+          <t>246873</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>303258</t>
+          <t>304501</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>411967</t>
+          <t>417321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>488146</t>
+          <t>490315</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>534219</t>
+          <t>530231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>576157</t>
+          <t>574052</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>483347</t>
+          <t>482333</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>528541</t>
+          <t>527265</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1031427</t>
+          <t>1034384</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1094472</t>
+          <t>1094290</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17972</t>
+          <t>17106</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25215</t>
+          <t>25652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98253</t>
+          <t>99053</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138576</t>
+          <t>141777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145448</t>
+          <t>145690</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190408</t>
+          <t>190611</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254135</t>
+          <t>252056</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315123</t>
+          <t>311410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>783097</t>
+          <t>782446</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>823263</t>
+          <t>824025</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>784024</t>
+          <t>781148</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>837277</t>
+          <t>837084</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1580615</t>
+          <t>1576671</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1648420</t>
+          <t>1649019</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,29%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>22222</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26964</t>
+          <t>27346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>114123</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>154686</t>
+          <t>154184</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>189167</t>
+          <t>189426</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>240383</t>
+          <t>246093</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>316306</t>
+          <t>315514</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>381111</t>
+          <t>385228</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2672920</t>
+          <t>2669896</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2760435</t>
+          <t>2755163</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2505396</t>
+          <t>2508669</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2603393</t>
+          <t>2605463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5203123</t>
+          <t>5199808</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5334483</t>
+          <t>5337484</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31592</t>
+          <t>30285</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25187</t>
+          <t>25301</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50323</t>
+          <t>49881</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41643</t>
+          <t>41446</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71984</t>
+          <t>71617</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>496109</t>
+          <t>500866</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>585024</t>
+          <t>584583</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>742014</t>
+          <t>735146</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>839809</t>
+          <t>833843</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1265979</t>
+          <t>1262898</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1392780</t>
+          <t>1398898</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>537540</t>
+          <t>538575</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>583887</t>
+          <t>581101</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>478422</t>
+          <t>478091</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>526132</t>
+          <t>528139</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1034252</t>
+          <t>1035833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1096271</t>
+          <t>1097951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15022</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21090</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113308</t>
+          <t>113962</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>157597</t>
+          <t>157229</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>165963</t>
+          <t>164843</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>213508</t>
+          <t>214919</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>290932</t>
+          <t>289652</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>352708</t>
+          <t>353382</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>760767</t>
+          <t>761318</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>814915</t>
+          <t>816461</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>699690</t>
+          <t>700343</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>761299</t>
+          <t>758664</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1480679</t>
+          <t>1476453</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1564145</t>
+          <t>1558858</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,04%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>14365</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>14505</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36928</t>
+          <t>36874</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20711</t>
+          <t>20991</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>44530</t>
+          <t>44865</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>195272</t>
+          <t>195767</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>249461</t>
+          <t>250419</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>248825</t>
+          <t>247889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>307588</t>
+          <t>306229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>456495</t>
+          <t>462001</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>538029</t>
+          <t>541672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>546964</t>
+          <t>548700</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>598257</t>
+          <t>596861</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>491544</t>
+          <t>490084</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>545495</t>
+          <t>544352</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1052134</t>
+          <t>1054915</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1126099</t>
+          <t>1127915</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,54%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18498</t>
+          <t>17673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19320</t>
+          <t>19517</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31473</t>
+          <t>32028</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150810</t>
+          <t>150315</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200879</t>
+          <t>198890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219837</t>
+          <t>221926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274437</t>
+          <t>274022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>386073</t>
+          <t>385512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>460021</t>
+          <t>458445</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>769457</t>
+          <t>768671</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>816214</t>
+          <t>817078</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>795249</t>
+          <t>795361</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>848557</t>
+          <t>849467</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1579378</t>
+          <t>1579779</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1653600</t>
+          <t>1649922</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,68%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16969</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>22355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15221</t>
+          <t>15774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34578</t>
+          <t>34963</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>119311</t>
+          <t>119646</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>165864</t>
+          <t>167030</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>189808</t>
+          <t>186213</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>240047</t>
+          <t>239101</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>319982</t>
+          <t>322538</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>391860</t>
+          <t>391919</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2665805</t>
+          <t>2670441</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2763114</t>
+          <t>2770323</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2512312</t>
+          <t>2514979</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2626234</t>
+          <t>2623825</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5214702</t>
+          <t>5214272</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5365185</t>
+          <t>5361408</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24762</t>
+          <t>24861</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47808</t>
+          <t>48711</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40974</t>
+          <t>40074</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70123</t>
+          <t>68801</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>71344</t>
+          <t>72051</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>108278</t>
+          <t>108119</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>625178</t>
+          <t>623013</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>719993</t>
+          <t>718609</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>876962</t>
+          <t>878723</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>986990</t>
+          <t>988899</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1520447</t>
+          <t>1529796</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1673178</t>
+          <t>1673569</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>547016</t>
+          <t>548951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>584302</t>
+          <t>587061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>507657</t>
+          <t>509988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>551391</t>
+          <t>552118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1066658</t>
+          <t>1067833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1127558</t>
+          <t>1123887</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,52%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18676</t>
+          <t>19717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>31071</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77726</t>
+          <t>76220</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113390</t>
+          <t>112414</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,82 +5998,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>16,71%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>131884</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>112877</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>153474</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>19,6%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>16,78%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>22,81%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>226683</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>202206</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>256444</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>16,85%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>131884</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>111746</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154440</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>19,6%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>16,61%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>22,95%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>226683</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>197165</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>257098</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>16,85%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>812707</t>
+          <t>816693</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>864693</t>
+          <t>866521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>792572</t>
+          <t>794433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>846938</t>
+          <t>848103</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1622955</t>
+          <t>1626480</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1697964</t>
+          <t>1700739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27355</t>
+          <t>27434</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30886</t>
+          <t>29856</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>24993</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>49967</t>
+          <t>51088</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134675</t>
+          <t>134843</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183074</t>
+          <t>181752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>176070</t>
+          <t>174591</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>226554</t>
+          <t>227170</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>323469</t>
+          <t>322092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>396065</t>
+          <t>394494</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>606367</t>
+          <t>609166</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>651193</t>
+          <t>651158</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>604415</t>
+          <t>606259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>649604</t>
+          <t>652722</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1225419</t>
+          <t>1225959</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1288721</t>
+          <t>1288092</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,52%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>13893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,82 +6797,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>10343</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5308</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>20558</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>16969</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>9906</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>27062</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>1,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10343</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5115</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18602</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>16969</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>9912</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>27560</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101471</t>
+          <t>100454</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>145588</t>
+          <t>142997</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122980</t>
+          <t>122175</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167009</t>
+          <t>167515</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>237821</t>
+          <t>237562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>299946</t>
+          <t>300444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>757443</t>
+          <t>755681</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>804105</t>
+          <t>801627</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>762587</t>
+          <t>766441</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>818547</t>
+          <t>822023</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1538079</t>
+          <t>1538244</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1612116</t>
+          <t>1608569</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,34%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14702</t>
+          <t>14237</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34163</t>
+          <t>33763</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>24014</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47605</t>
+          <t>47947</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>121378</t>
+          <t>124161</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>166309</t>
+          <t>168314</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>199206</t>
+          <t>196855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>255584</t>
+          <t>250094</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>334110</t>
+          <t>336120</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>405517</t>
+          <t>407850</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2778181</t>
+          <t>2772776</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2862451</t>
+          <t>2858318</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2720750</t>
+          <t>2724242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2823808</t>
+          <t>2824294</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5529828</t>
+          <t>5522158</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5664986</t>
+          <t>5657200</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61269</t>
+          <t>61179</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44524</t>
+          <t>45343</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78948</t>
+          <t>78712</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>87875</t>
+          <t>88782</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>132022</t>
+          <t>131209</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>479418</t>
+          <t>480312</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>559088</t>
+          <t>563714</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>655834</t>
+          <t>657122</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>758355</t>
+          <t>754292</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1156904</t>
+          <t>1160472</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1286180</t>
+          <t>1287024</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>505057</t>
+          <t>550210</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>482300</t>
+          <t>526082</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>525958</t>
+          <t>572278</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>532658</t>
+          <t>579429</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>514849</t>
+          <t>560993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>550313</t>
+          <t>598103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1037716</t>
+          <t>1129639</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1008949</t>
+          <t>1101563</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1061880</t>
+          <t>1158822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -8377,67 +8377,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>353</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4137</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8160</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3827</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1725</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6689</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,17 +8447,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>126917</t>
+          <t>136712</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106418</t>
+          <t>114102</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149732</t>
+          <t>160832</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139268</t>
+          <t>149546</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>122601</t>
+          <t>131589</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158019</t>
+          <t>168107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>266185</t>
+          <t>286259</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>241879</t>
+          <t>256881</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>295699</t>
+          <t>313931</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>633688</t>
+          <t>688739</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>633688</t>
+          <t>688739</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>633688</t>
+          <t>688739</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1309441</t>
+          <t>1421852</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1309441</t>
+          <t>1421852</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1309441</t>
+          <t>1421852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>979183</t>
+          <t>814550</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>914314</t>
+          <t>783684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1090663</t>
+          <t>844714</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>720195</t>
+          <t>808207</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>697187</t>
+          <t>780499</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>744320</t>
+          <t>832946</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1699378</t>
+          <t>1622757</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1627541</t>
+          <t>1576912</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1863026</t>
+          <t>1661152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16353</t>
+          <t>17451</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>210154</t>
+          <t>230706</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>100687</t>
+          <t>201050</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>275169</t>
+          <t>262423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>230314</t>
+          <t>254313</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>207005</t>
+          <t>230315</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>253791</t>
+          <t>281330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>440468</t>
+          <t>485019</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>279365</t>
+          <t>447083</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>511133</t>
+          <t>529951</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>956331</t>
+          <t>1068913</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>956331</t>
+          <t>1068913</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>956331</t>
+          <t>1068913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2149195</t>
+          <t>2117830</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2149195</t>
+          <t>2117830</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2149195</t>
+          <t>2117830</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>565111</t>
+          <t>650274</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>538212</t>
+          <t>621909</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>586950</t>
+          <t>674463</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>539782</t>
+          <t>590443</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>286147</t>
+          <t>566658</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>701578</t>
+          <t>613204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1104893</t>
+          <t>1240716</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>769195</t>
+          <t>1204459</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1279312</t>
+          <t>1274680</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>134391</t>
+          <t>147220</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112096</t>
+          <t>123195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161287</t>
+          <t>174930</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>387912</t>
+          <t>215348</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224927</t>
+          <t>192049</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>640082</t>
+          <t>239257</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>522303</t>
+          <t>362568</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>347029</t>
+          <t>329741</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>860051</t>
+          <t>397675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>929546</t>
+          <t>808414</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>929546</t>
+          <t>808414</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>929546</t>
+          <t>808414</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1634226</t>
+          <t>1611487</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1634226</t>
+          <t>1611487</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1634226</t>
+          <t>1611487</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>731788</t>
+          <t>782575</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>703844</t>
+          <t>753933</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>755402</t>
+          <t>808734</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>814570</t>
+          <t>815358</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>783400</t>
+          <t>787938</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>872514</t>
+          <t>839755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1546357</t>
+          <t>1597933</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1503899</t>
+          <t>1559245</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1600030</t>
+          <t>1634181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>77,53%</t>
         </is>
       </c>
     </row>
@@ -9745,17 +9745,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16370</t>
+          <t>19040</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>28733</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>28714</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17490</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35584</t>
+          <t>41453</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -9858,27 +9858,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>185995</t>
+          <t>197812</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>160829</t>
+          <t>172707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>212387</t>
+          <t>226895</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>261122</t>
+          <t>283329</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207389</t>
+          <t>258835</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>289500</t>
+          <t>310987</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>447118</t>
+          <t>481141</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>396334</t>
+          <t>444645</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>488440</t>
+          <t>518453</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1092062</t>
+          <t>1117726</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1092062</t>
+          <t>1117726</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1092062</t>
+          <t>1117726</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2018893</t>
+          <t>2107788</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2018893</t>
+          <t>2107788</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2018893</t>
+          <t>2107788</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2781140</t>
+          <t>2797610</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2702110</t>
+          <t>2744189</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2933540</t>
+          <t>2850242</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2607205</t>
+          <t>2793437</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2118192</t>
+          <t>2749218</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2779790</t>
+          <t>2839288</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5388344</t>
+          <t>5591047</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4788190</t>
+          <t>5515804</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5585163</t>
+          <t>5660354</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -10201,67 +10201,67 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19467</t>
+          <t>20730</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>13779</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29856</t>
+          <t>29299</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>32194</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>24033</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>42959</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>27870</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>19935</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>37392</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>47337</t>
+          <t>52925</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>42418</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>61174</t>
+          <t>65876</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>657457</t>
+          <t>712452</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>509372</t>
+          <t>658173</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>735800</t>
+          <t>765278</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1018616</t>
+          <t>902535</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>843271</t>
+          <t>856225</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1507931</t>
+          <t>945619</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1676074</t>
+          <t>1614987</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1479337</t>
+          <t>1545399</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2298887</t>
+          <t>1687288</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3458064</t>
+          <t>3530792</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3653691</t>
+          <t>3728166</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7111755</t>
+          <t>7258958</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
